--- a/config/配置_v2.0.xlsx
+++ b/config/配置_v2.0.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22010" windowHeight="12332" activeTab="2"/>
+    <workbookView windowWidth="22010" windowHeight="12332" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="project" sheetId="1" r:id="rId1"/>
-    <sheet name="devices" sheetId="2" r:id="rId2"/>
-    <sheet name="config" sheetId="4" r:id="rId3"/>
-    <sheet name="mqtt_routes" sheetId="5" r:id="rId4"/>
+    <sheet name="program" sheetId="6" r:id="rId2"/>
+    <sheet name="devices" sheetId="2" r:id="rId3"/>
+    <sheet name="config" sheetId="4" r:id="rId4"/>
+    <sheet name="mqtt_routes" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="109">
   <si>
     <t>key</t>
   </si>
@@ -59,13 +60,28 @@
     <t>项目名称：</t>
   </si>
   <si>
-    <t>emu_enable</t>
-  </si>
-  <si>
-    <t>是否启用EMU功能</t>
-  </si>
-  <si>
-    <t>http_ip</t>
+    <t>feature</t>
+  </si>
+  <si>
+    <t>param</t>
+  </si>
+  <si>
+    <t>param_desc</t>
+  </si>
+  <si>
+    <t>extra</t>
+  </si>
+  <si>
+    <t>enable</t>
+  </si>
+  <si>
+    <t>EMU特性</t>
+  </si>
+  <si>
+    <t>HTTP</t>
+  </si>
+  <si>
+    <t>ip</t>
   </si>
   <si>
     <t>0.0.0.0</t>
@@ -74,16 +90,61 @@
     <t>HTTP监听IP</t>
   </si>
   <si>
-    <t>http_port</t>
+    <t>HTTP接口</t>
+  </si>
+  <si>
+    <t>port</t>
   </si>
   <si>
     <t>HTTP监听端口</t>
   </si>
   <si>
-    <t>mqtt_enable</t>
-  </si>
-  <si>
-    <t>是否启用MQTT</t>
+    <t>MOD</t>
+  </si>
+  <si>
+    <t>path</t>
+  </si>
+  <si>
+    <t>lua_scripts</t>
+  </si>
+  <si>
+    <t>启用脚本引擎</t>
+  </si>
+  <si>
+    <t>NORTH_MODBUS</t>
+  </si>
+  <si>
+    <t>north_modbus_host</t>
+  </si>
+  <si>
+    <t>北向Modbus从机IP</t>
+  </si>
+  <si>
+    <t>启用北向MODBUS协议</t>
+  </si>
+  <si>
+    <t>north_modbus_port</t>
+  </si>
+  <si>
+    <t>北向Modbus从机端口</t>
+  </si>
+  <si>
+    <t>north_modbus_conf</t>
+  </si>
+  <si>
+    <t>./config/MODBUS_REGISTERS.xlsx</t>
+  </si>
+  <si>
+    <t>北向Modbus配置文件</t>
+  </si>
+  <si>
+    <t>EG25-GL</t>
+  </si>
+  <si>
+    <t>启用移远4G</t>
+  </si>
+  <si>
+    <t>MQTT</t>
   </si>
   <si>
     <t>mqtt_host</t>
@@ -95,6 +156,9 @@
     <t>MQTT服务器地址</t>
   </si>
   <si>
+    <t>启用MQTT</t>
+  </si>
+  <si>
     <t>mqtt_port</t>
   </si>
   <si>
@@ -137,27 +201,6 @@
     <t>MQTT遥控</t>
   </si>
   <si>
-    <t>north_modbus_host</t>
-  </si>
-  <si>
-    <t>北向Modbus从机IP</t>
-  </si>
-  <si>
-    <t>north_modbus_port</t>
-  </si>
-  <si>
-    <t>北向Modbus从机端口</t>
-  </si>
-  <si>
-    <t>north_modbus_conf</t>
-  </si>
-  <si>
-    <t>./config/MODBUS_REGISTERS.xlsx</t>
-  </si>
-  <si>
-    <t>北向Modbus配置文件</t>
-  </si>
-  <si>
     <t>no</t>
   </si>
   <si>
@@ -236,12 +279,6 @@
     <t>timeout</t>
   </si>
   <si>
-    <t>ip</t>
-  </si>
-  <si>
-    <t>port</t>
-  </si>
-  <si>
     <t>slave</t>
   </si>
   <si>
@@ -321,9 +358,6 @@
   </si>
   <si>
     <t>point_ids</t>
-  </si>
-  <si>
-    <t>enable</t>
   </si>
 </sst>
 </file>
@@ -336,7 +370,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -353,23 +387,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="微软雅黑"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -851,156 +873,162 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1314,8 +1342,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultColWidth="22.4047619047619" defaultRowHeight="18" outlineLevelCol="2"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultColWidth="22.4047619047619" defaultRowHeight="18" outlineLevelRow="2" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="22.4047619047619" style="4"/>
     <col min="2" max="2" width="33.7936507936508" style="4" customWidth="1"/>
@@ -1323,13 +1351,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1353,149 +1381,6 @@
       </c>
       <c r="C3" s="4" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="4">
-        <v>9091</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="4">
-        <v>1883</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="4">
-        <v>9092</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1506,6 +1391,248 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr defaultColWidth="9.03174603174603" defaultRowHeight="18" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="17.5238095238095" style="7" customWidth="1"/>
+    <col min="2" max="2" width="19.0079365079365" style="7" customWidth="1"/>
+    <col min="3" max="3" width="31.1825396825397" style="7" customWidth="1"/>
+    <col min="4" max="4" width="19.1428571428571" style="7" customWidth="1"/>
+    <col min="5" max="6" width="10.4206349206349" style="7" customWidth="1"/>
+    <col min="7" max="7" width="20.6666666666667" style="7" customWidth="1"/>
+    <col min="8" max="16384" width="9.03174603174603" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="7" customFormat="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" s="8" customFormat="1" spans="1:7">
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" s="8" customFormat="1" spans="1:7">
+      <c r="A3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" s="8" customFormat="1" spans="1:7">
+      <c r="B4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="8">
+        <v>9091</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" s="8" customFormat="1" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" s="8" customFormat="1" spans="1:7">
+      <c r="A6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" s="8" customFormat="1" spans="1:7">
+      <c r="B7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="4">
+        <v>9092</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" s="8" customFormat="1" spans="1:7">
+      <c r="B8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" s="8" customFormat="1" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" s="8" customFormat="1" spans="1:7">
+      <c r="A10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" s="8" customFormat="1" spans="1:7">
+      <c r="B11" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="4">
+        <v>1883</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" s="8" customFormat="1" spans="1:7">
+      <c r="B12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" s="8" customFormat="1" spans="1:7">
+      <c r="B13" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" s="8" customFormat="1" spans="1:7">
+      <c r="B14" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" s="8" customFormat="1" spans="1:7">
+      <c r="B15" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="A10:A15"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="F10:F15"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G6:G8"/>
+    <mergeCell ref="G10:G15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:E7"/>
@@ -1518,18 +1645,18 @@
     <col min="5" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="3" customFormat="1" spans="1:5">
-      <c r="A1" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>45</v>
+    <row r="1" s="1" customFormat="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="E1" s="4"/>
     </row>
@@ -1538,13 +1665,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1552,13 +1679,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1566,13 +1693,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1580,13 +1707,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1594,13 +1721,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1608,13 +1735,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1624,7 +1751,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:S7"/>
@@ -1643,63 +1770,63 @@
     <col min="19" max="16384" width="9.07142857142857" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="3" customFormat="1" spans="1:19">
-      <c r="A1" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>70</v>
+    <row r="1" s="1" customFormat="1" spans="1:19">
+      <c r="A1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>78</v>
+        <v>88</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:19">
@@ -1707,16 +1834,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F2" s="4">
         <v>1000</v>
@@ -1725,7 +1852,7 @@
         <v>2000</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="I2" s="4">
         <v>502</v>
@@ -1739,16 +1866,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F3" s="4">
         <v>2000</v>
@@ -1763,7 +1890,7 @@
         <v>500000</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1771,16 +1898,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="F4" s="4">
         <v>2000</v>
@@ -1792,7 +1919,7 @@
         <v>2</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="L4" s="4">
         <v>9600</v>
@@ -1801,7 +1928,7 @@
         <v>8</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="O4" s="4">
         <v>1</v>
@@ -1812,16 +1939,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="F5" s="4">
         <v>2000</v>
@@ -1833,7 +1960,7 @@
         <v>1</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="L5" s="4">
         <v>9600</v>
@@ -1842,7 +1969,7 @@
         <v>8</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="O5" s="4">
         <v>1</v>
@@ -1853,16 +1980,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="F6" s="4">
         <v>2000</v>
@@ -1874,7 +2001,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="L6" s="4">
         <v>9600</v>
@@ -1883,7 +2010,7 @@
         <v>8</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="O6" s="4">
         <v>1</v>
@@ -1894,16 +2021,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="F7" s="4">
         <v>2000</v>
@@ -1919,38 +2046,43 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18" outlineLevelCol="6"/>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18" outlineLevelRow="5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="11.7619047619048" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.6746031746032" style="2" customWidth="1"/>
-    <col min="3" max="3" width="144.857142857143" style="2" customWidth="1"/>
-    <col min="4" max="4" width="20.3968253968254" style="2" customWidth="1"/>
-    <col min="5" max="5" width="10.2936507936508" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.4365079365079" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.11111111111111" style="2"/>
+    <col min="1" max="1" width="11.7619047619048" style="3" customWidth="1"/>
+    <col min="2" max="2" width="20.6746031746032" style="3" customWidth="1"/>
+    <col min="3" max="3" width="144.857142857143" style="3" customWidth="1"/>
+    <col min="4" max="4" width="20.3968253968254" style="3" customWidth="1"/>
+    <col min="5" max="5" width="10.2936507936508" style="3" customWidth="1"/>
+    <col min="6" max="6" width="10.4365079365079" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="9.11111111111111" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
+        <v>13</v>
+      </c>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" s="2" customFormat="1"/>
+    <row r="3" s="2" customFormat="1"/>
+    <row r="4" s="2" customFormat="1"/>
+    <row r="5" s="2" customFormat="1"/>
+    <row r="6" s="2" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
